--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -8360,7 +8360,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://mongodb.com/careers</t>
+          <t>https://mongodb.com/jobs</t>
         </is>
       </c>
       <c r="E255" t="b">
@@ -12890,7 +12890,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://www.udacity.com/jobs</t>
+          <t>https://www.udacity.com/careers</t>
         </is>
       </c>
       <c r="E401" t="b">
@@ -13417,13 +13417,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>https://wildbit.com/jobs</t>
-        </is>
-      </c>
+      <c r="D418" t="inlineStr"/>
       <c r="E418" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -1201,9 +1201,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.audiense.com/careers</t>
+        </is>
+      </c>
       <c r="E26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1841,9 +1845,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://bizinkonline.com/careers</t>
+        </is>
+      </c>
       <c r="E46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2737,9 +2745,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.cloudlinux.com/careers</t>
+        </is>
+      </c>
       <c r="E74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4180,9 +4192,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://earthofdrones.com/careers</t>
+        </is>
+      </c>
       <c r="E121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -5197,13 +5213,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>https://folotop.com/careers</t>
-        </is>
-      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -8360,7 +8372,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://mongodb.com/jobs</t>
+          <t>https://mongodb.com/careers</t>
         </is>
       </c>
       <c r="E255" t="b">
@@ -8587,7 +8599,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>['senior software engineer - pythoncontractpolandremote (https://job-boards.greenhouse.io/nearform/jobs/7680255003)', 'senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'senior software engineer - python &amp; aipermanentirelandremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7653769003)', 'senior software engineer - python &amp; aipermanentukremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631240003)', 'senior software engineer - python &amp; aipermanentitalyremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631320003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)']</t>
+          <t>['senior software engineer - pythoncontractpolandremote (https://job-boards.greenhouse.io/nearform/jobs/7680255003)', 'senior software engineer - python &amp; aipermanentirelandremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7653769003)', 'senior software engineer - python &amp; aipermanentukremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631240003)', 'senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'senior software engineer - python &amp; aipermanentitalyremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631320003)', 'senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)']</t>
         </is>
       </c>
       <c r="G262" t="b">
@@ -10305,13 +10317,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>https://redliodesigns.com/careers</t>
-        </is>
-      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -13417,9 +13425,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>https://wildbit.com/jobs</t>
+        </is>
+      </c>
       <c r="E418" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -1201,13 +1201,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://www.audiense.com/careers</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1845,13 +1841,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>https://bizinkonline.com/careers</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2745,13 +2737,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>https://www.cloudlinux.com/careers</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3132,7 +3120,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://consensys.net/careers</t>
+          <t>https://consensys.net/jobs</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -4192,13 +4180,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>https://earthofdrones.com/careers</t>
-        </is>
-      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -5213,9 +5197,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>https://folotop.com/careers</t>
+        </is>
+      </c>
       <c r="E154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -8599,7 +8587,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>['senior software engineer - pythoncontractpolandremote (https://job-boards.greenhouse.io/nearform/jobs/7680255003)', 'senior software engineer - python &amp; aipermanentirelandremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7653769003)', 'senior software engineer - python &amp; aipermanentukremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631240003)', 'senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'senior software engineer - python &amp; aipermanentitalyremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631320003)', 'senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)']</t>
+          <t>['senior software engineer - pythoncontractpolandremote (https://job-boards.greenhouse.io/nearform/jobs/7680255003)', 'senior software engineer - python &amp; aipermanentirelandremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7653769003)', 'senior software engineer - python &amp; aipermanentitalyremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631320003)', 'senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'senior software engineer - python &amp; aipermanentukremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631240003)', 'senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)']</t>
         </is>
       </c>
       <c r="G262" t="b">
@@ -10317,9 +10305,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>https://redliodesigns.com/careers</t>
+        </is>
+      </c>
       <c r="E318" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -8453,13 +8453,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>https://mvpmule.com/careers</t>
-        </is>
-      </c>
+      <c r="D258" t="inlineStr"/>
       <c r="E258" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -8587,7 +8583,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>['senior software engineer - pythoncontractpolandremote (https://job-boards.greenhouse.io/nearform/jobs/7680255003)', 'senior software engineer - python &amp; aipermanentirelandremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7653769003)', 'senior software engineer - python &amp; aipermanentitalyremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631320003)', 'senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'senior software engineer - python &amp; aipermanentukremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631240003)', 'senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)']</t>
+          <t>['senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'senior software engineer - python &amp; aipermanentukremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631240003)', 'senior software engineer - python &amp; aipermanentitalyremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631320003)', 'senior software engineer - python &amp; aipermanentirelandremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7653769003)', 'senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)']</t>
         </is>
       </c>
       <c r="G262" t="b">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -4595,11 +4595,11 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['data scientist ic3.1dublin, irelanddata science &amp; machine learning (https://careers.etsy.com/jobs/data-scientist-ic3-1-dublin-ireland)']</t>
         </is>
       </c>
       <c r="G134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -8453,9 +8453,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>https://mvpmule.com/careers</t>
+        </is>
+      </c>
       <c r="E258" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -13390,11 +13394,11 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['senior data scientist, safety &amp; security (https://grnh.se/jfz19iis1us)']</t>
         </is>
       </c>
       <c r="G417" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="418">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -7666,11 +7666,11 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['senior cloud developer (python/azure/fabric/purview)remote india, indiasoftware/system architecture (https://www.luxoft.com/careers/jobs/senior-cloud-developer-pythonazurefabricpurview-27568)']</t>
         </is>
       </c>
       <c r="G233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>['senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'senior software engineer - python &amp; aipermanentukremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631240003)', 'senior software engineer - python &amp; aipermanentitalyremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631320003)', 'senior software engineer - python &amp; aipermanentirelandremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7653769003)', 'senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)']</t>
+          <t>['senior software engineer - python &amp; aipermanentirelandremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7653769003)', 'senior software engineer - python &amp; aipermanentukremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631240003)', 'senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'senior software engineer - python &amp; aipermanentitalyremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631320003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)']</t>
         </is>
       </c>
       <c r="G262" t="b">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -4595,11 +4595,11 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>['data scientist ic3.1dublin, irelanddata science &amp; machine learning (https://careers.etsy.com/jobs/data-scientist-ic3-1-dublin-ireland)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -5759,13 +5759,9 @@
           <t>usa / worldwide</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>https://www.grubhub.com/careers</t>
-        </is>
-      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -7666,11 +7662,11 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>['senior cloud developer (python/azure/fabric/purview)remote india, indiasoftware/system architecture (https://www.luxoft.com/careers/jobs/senior-cloud-developer-pythonazurefabricpurview-27568)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G233" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -8587,7 +8583,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>['senior software engineer - python &amp; aipermanentirelandremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7653769003)', 'senior software engineer - python &amp; aipermanentukremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631240003)', 'senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'senior software engineer - python &amp; aipermanentitalyremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7631320003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)']</t>
+          <t>['senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)']</t>
         </is>
       </c>
       <c r="G262" t="b">
@@ -12512,13 +12508,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>https://thewirecutter.com/jobs</t>
-        </is>
-      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -502,13 +502,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://37signals.com/jobs</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1585,13 +1581,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://basecamp.com/jobs</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2998,13 +2990,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>https://www.collabora.com/careers</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -5197,13 +5185,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>https://folotop.com/careers</t>
-        </is>
-      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -5759,9 +5743,13 @@
           <t>usa / worldwide</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>https://www.grubhub.com/careers</t>
+        </is>
+      </c>
       <c r="E172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -7662,11 +7650,11 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['senior mlops engineer / data scientistremote india, indiaai/ml (https://www.luxoft.com/careers/jobs/senior-mlops-engineer-data-scientist-27710)', 'senior mlops engineer / data scientistremote india, indiaai/ml (https://www.luxoft.com/careers/jobs/senior-mlops-engineer-data-scientist-27709)', 'senior mlops engineer / data scientistremote india, indiaai/ml (https://www.luxoft.com/careers/jobs/senior-mlops-engineer-data-scientist-27708)', 'senior mlops engineer / data scientistremote india, indiaai/ml (https://www.luxoft.com/careers/jobs/senior-mlops-engineer-data-scientist-27707)']</t>
         </is>
       </c>
       <c r="G233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
@@ -7761,11 +7749,11 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>['senior data scientist (https://job-boards.eu.greenhouse.io/mariadbplc/jobs/4806320101)', 'senior data scientist (https://job-boards.eu.greenhouse.io/mariadbplc/jobs/4829004101)', 'senior data scientist (https://job-boards.eu.greenhouse.io/mariadbplc/jobs/4829008101)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G236" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -10301,13 +10289,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>https://redliodesigns.com/careers</t>
-        </is>
-      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -502,9 +502,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://37signals.com/jobs</t>
+        </is>
+      </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1581,9 +1585,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://basecamp.com/jobs</t>
+        </is>
+      </c>
       <c r="E38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2903,9 +2911,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://codeship.com/jobs</t>
+        </is>
+      </c>
       <c r="E80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2990,9 +3002,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.collabora.com/careers</t>
+        </is>
+      </c>
       <c r="E83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -5185,9 +5201,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>https://folotop.com/careers</t>
+        </is>
+      </c>
       <c r="E154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -7650,11 +7670,11 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>['senior mlops engineer / data scientistremote india, indiaai/ml (https://www.luxoft.com/careers/jobs/senior-mlops-engineer-data-scientist-27710)', 'senior mlops engineer / data scientistremote india, indiaai/ml (https://www.luxoft.com/careers/jobs/senior-mlops-engineer-data-scientist-27709)', 'senior mlops engineer / data scientistremote india, indiaai/ml (https://www.luxoft.com/careers/jobs/senior-mlops-engineer-data-scientist-27708)', 'senior mlops engineer / data scientistremote india, indiaai/ml (https://www.luxoft.com/careers/jobs/senior-mlops-engineer-data-scientist-27707)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G233" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -7836,7 +7856,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://meant4.com/careers</t>
+          <t>https://meant4.com/jobs</t>
         </is>
       </c>
       <c r="E239" t="b">
@@ -10289,9 +10309,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>https://redliodesigns.com/careers</t>
+        </is>
+      </c>
       <c r="E318" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -1339,11 +1339,11 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['backend engineer - python (remote - india)remotefull-timeopen nowbuild backend systems that make complex workflows reliable, maintainable, and easier to evolve. you’ll work on production python services, modernize existing applications, and deliver apis and integrations used by real teams. the role is focused on backend development using pytho...view role (https://axelerant.com/careers/careers/backend-engineer-python-remote-india)']</t>
         </is>
       </c>
       <c r="G30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -4599,11 +4599,11 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['senior data scientist, ads marketplacebrooklyn, brooklyn heights, new york, united states, 11201analytics (https://careers.etsy.com/jobs/senior-data-scientist-ads-marketplace-brooklyn-new-york-united-states)']</t>
         </is>
       </c>
       <c r="G134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>['senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)']</t>
+          <t>['senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)']</t>
         </is>
       </c>
       <c r="G262" t="b">
@@ -11524,13 +11524,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>https://www.skyrocketventures.com/careers</t>
-        </is>
-      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -3002,13 +3002,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>https://www.collabora.com/careers</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -4308,13 +4304,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>https://www.emsisoft.com/careers</t>
-        </is>
-      </c>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10937,21 +10929,17 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>https://scrapinghub.com/careers</t>
-        </is>
-      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>['web scraping in python: ultimate guide (https://scrapinghub.com/careers/blog/web-scraping-in-python-ultimate-guide/)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G338" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
@@ -11524,9 +11512,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>https://www.skyrocketventures.com/careers</t>
+        </is>
+      </c>
       <c r="E357" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -12489,11 +12481,11 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['senior full stack python/react engineer – aws / investment technology (https://careers.theplanetgroup.com/job/652372-senior-full-stack-python-react-engineer-aws-investment-technology-malvern-pennsylvania/)']</t>
         </is>
       </c>
       <c r="G388" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="389">
@@ -12665,17 +12657,21 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>https://www.toptal.com/careers</t>
+        </is>
+      </c>
       <c r="E394" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['python developers (https://www.toptal.com/careers/developers/python)', 'python developers (https://www.toptal.com/careers/developers/python)']</t>
         </is>
       </c>
       <c r="G394" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -1201,9 +1201,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.audiense.com/careers</t>
+        </is>
+      </c>
       <c r="E26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1841,9 +1845,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://bizinkonline.com/careers</t>
+        </is>
+      </c>
       <c r="E46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3002,9 +3010,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.collabora.com/careers</t>
+        </is>
+      </c>
       <c r="E83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -4180,9 +4192,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://earthofdrones.com/careers</t>
+        </is>
+      </c>
       <c r="E121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -4304,9 +4320,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://www.emsisoft.com/careers</t>
+        </is>
+      </c>
       <c r="E125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -5193,13 +5213,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>https://folotop.com/careers</t>
-        </is>
-      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -10301,13 +10317,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>https://redliodesigns.com/careers</t>
-        </is>
-      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -10929,17 +10941,21 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>https://scrapinghub.com/careers</t>
+        </is>
+      </c>
       <c r="E338" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['web scraping in python: ultimate guide (https://scrapinghub.com/careers/blog/web-scraping-in-python-ultimate-guide/)']</t>
         </is>
       </c>
       <c r="G338" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
@@ -12481,11 +12497,11 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>['senior full stack python/react engineer – aws / investment technology (https://careers.theplanetgroup.com/job/652372-senior-full-stack-python-react-engineer-aws-investment-technology-malvern-pennsylvania/)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G388" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="389">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -1201,13 +1201,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://www.audiense.com/careers</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1845,13 +1841,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>https://bizinkonline.com/careers</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4192,13 +4184,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>https://earthofdrones.com/careers</t>
-        </is>
-      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -5213,9 +5201,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>https://folotop.com/careers</t>
+        </is>
+      </c>
       <c r="E154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -9984,7 +9976,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://rackspace.com/careers</t>
+          <t>https://rackspace.com/jobs</t>
         </is>
       </c>
       <c r="E307" t="b">
@@ -10317,9 +10309,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>https://redliodesigns.com/careers</t>
+        </is>
+      </c>
       <c r="E318" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -9976,7 +9976,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://rackspace.com/jobs</t>
+          <t>https://rackspace.com/careers</t>
         </is>
       </c>
       <c r="E307" t="b">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -12925,9 +12925,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>https://uhurunetwork.com/careers</t>
+        </is>
+      </c>
       <c r="E402" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -13045,13 +13049,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>https://www.varnish-software.com/about-us/careers</t>
-        </is>
-      </c>
+      <c r="D406" t="inlineStr"/>
       <c r="E406" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -4599,11 +4599,11 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>['senior data scientist, ads marketplacebrooklyn, brooklyn heights, new york, united states, 11201analytics (https://careers.etsy.com/jobs/senior-data-scientist-ads-marketplace-brooklyn-new-york-united-states)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://www.skyrocketventures.com/careers</t>
+          <t>https://www.skyrocketventures.com/jobs</t>
         </is>
       </c>
       <c r="E357" t="b">
@@ -12669,21 +12669,17 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>https://www.toptal.com/careers</t>
-        </is>
-      </c>
+      <c r="D394" t="inlineStr"/>
       <c r="E394" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>['python developers (https://www.toptal.com/careers/developers/python)', 'python developers (https://www.toptal.com/careers/developers/python)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G394" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395">
@@ -13049,9 +13045,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>https://www.varnish-software.com/about-us/careers</t>
+        </is>
+      </c>
       <c r="E406" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -6467,7 +6467,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://www.intuit.com/careers</t>
+          <t>https://www.intuit.com/jobs</t>
         </is>
       </c>
       <c r="E194" t="b">
@@ -7670,11 +7670,11 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['senior backend developer (ai, python)remote india, indiapython (https://www.luxoft.com/careers/jobs/senior-backend-developer-ai-python-28056)']</t>
         </is>
       </c>
       <c r="G233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://www.skyrocketventures.com/jobs</t>
+          <t>https://www.skyrocketventures.com/careers</t>
         </is>
       </c>
       <c r="E357" t="b">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -6467,7 +6467,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://www.intuit.com/jobs</t>
+          <t>https://www.intuit.com/careers</t>
         </is>
       </c>
       <c r="E194" t="b">
@@ -7670,11 +7670,11 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>['senior backend developer (ai, python)remote india, indiapython (https://www.luxoft.com/careers/jobs/senior-backend-developer-ai-python-28056)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G233" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://www.skyrocketventures.com/careers</t>
+          <t>https://www.skyrocketventures.com/jobs</t>
         </is>
       </c>
       <c r="E357" t="b">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -11526,7 +11526,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://www.skyrocketventures.com/jobs</t>
+          <t>https://www.skyrocketventures.com/careers</t>
         </is>
       </c>
       <c r="E357" t="b">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -6467,7 +6467,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://www.intuit.com/careers</t>
+          <t>https://www.intuit.com/jobs</t>
         </is>
       </c>
       <c r="E194" t="b">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -6467,7 +6467,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://www.intuit.com/jobs</t>
+          <t>https://www.intuit.com/careers</t>
         </is>
       </c>
       <c r="E194" t="b">
@@ -11524,13 +11524,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>https://www.skyrocketventures.com/careers</t>
-        </is>
-      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -11524,9 +11524,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>https://www.skyrocketventures.com/careers</t>
+        </is>
+      </c>
       <c r="E357" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -3242,13 +3242,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>https://creex.team/careers</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9976,7 +9972,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://rackspace.com/careers</t>
+          <t>https://rackspace.com/jobs</t>
         </is>
       </c>
       <c r="E307" t="b">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -3242,9 +3242,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://creex.team/careers</t>
+        </is>
+      </c>
       <c r="E91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -6118,9 +6122,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>https://hmn.md/careers</t>
+        </is>
+      </c>
       <c r="E183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -7666,11 +7674,11 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['senior qa automation engineerwroclaw, polandautomated testing python (https://www.luxoft.com/careers/jobs/senior-qa-automation-engineer-28240)', 'senior qa automation engineerkrakow, polandautomated testing python (https://www.luxoft.com/careers/jobs/senior-qa-automation-engineer-28239)']</t>
         </is>
       </c>
       <c r="G233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
@@ -9972,7 +9980,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://rackspace.com/jobs</t>
+          <t>https://rackspace.com/careers</t>
         </is>
       </c>
       <c r="E307" t="b">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -4599,11 +4599,11 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['data scientist, paymentsbrooklyn, brooklyn heights, new york, united states, 11201analytics (https://careers.etsy.com/jobs/data-scientist-payments-brooklyn-new-york-united-states)']</t>
         </is>
       </c>
       <c r="G134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -7674,11 +7674,11 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>['senior qa automation engineerwroclaw, polandautomated testing python (https://www.luxoft.com/careers/jobs/senior-qa-automation-engineer-28240)', 'senior qa automation engineerkrakow, polandautomated testing python (https://www.luxoft.com/careers/jobs/senior-qa-automation-engineer-28239)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G233" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -11530,7 +11530,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://www.skyrocketventures.com/careers</t>
+          <t>https://www.skyrocketventures.com/jobs</t>
         </is>
       </c>
       <c r="E357" t="b">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -11530,7 +11530,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://www.skyrocketventures.com/jobs</t>
+          <t>https://www.skyrocketventures.com/careers</t>
         </is>
       </c>
       <c r="E357" t="b">
@@ -12830,9 +12830,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>https://www.turing.com/recruitment</t>
+        </is>
+      </c>
       <c r="E399" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -1841,9 +1841,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://bizinkonline.com/join</t>
+        </is>
+      </c>
       <c r="E46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4599,11 +4603,11 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>['data scientist, paymentsbrooklyn, brooklyn heights, new york, united states, 11201analytics (https://careers.etsy.com/jobs/data-scientist-payments-brooklyn-new-york-united-states)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -5201,13 +5205,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>https://folotop.com/careers</t>
-        </is>
-      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://www.netguru.com/jobs</t>
+          <t>https://www.netguru.com/careers</t>
         </is>
       </c>
       <c r="E264" t="b">
@@ -8657,11 +8657,11 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['python (https://www.netguru.com/services/python-development)']</t>
         </is>
       </c>
       <c r="G264" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://rackspace.com/careers</t>
+          <t>https://rackspace.com/jobs</t>
         </is>
       </c>
       <c r="E307" t="b">
@@ -12830,13 +12830,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>https://www.turing.com/recruitment</t>
-        </is>
-      </c>
+      <c r="D399" t="inlineStr"/>
       <c r="E399" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -1841,13 +1841,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>https://bizinkonline.com/join</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5205,9 +5201,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>https://folotop.com/careers</t>
+        </is>
+      </c>
       <c r="E154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://rackspace.com/jobs</t>
+          <t>https://rackspace.com/careers</t>
         </is>
       </c>
       <c r="E307" t="b">
@@ -10513,11 +10513,11 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['data scientist, enterprisefoster city, ca·full-timeview job (https://replit.com/careers/jobs/c05749db-f413-4091-a95c-c8e0aa1b5630)', 'data scientist, growthfoster city, ca·full-timeview job (https://replit.com/careers/jobs/1066b974-3cd8-42cf-a11c-a4217c06f70f)']</t>
         </is>
       </c>
       <c r="G324" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -4403,13 +4403,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>https://envato.com/careers</t>
-        </is>
-      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -7674,11 +7670,11 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['senior test automation engineermadrid, spainautomated testing python (https://www.luxoft.com/careers/jobs/senior-test-automation-engineer-28419)']</t>
         </is>
       </c>
       <c r="G233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -4595,11 +4595,11 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['data scientist, trust and safety analyticsciudad de méxico, cdmx, mexico city, mexico, 06500analytics (https://careers.etsy.com/jobs/data-scientist-trust-and-safety-analytics-cdmx-mexico-city-mexico)']</t>
         </is>
       </c>
       <c r="G134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -7670,11 +7670,11 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>['senior test automation engineermadrid, spainautomated testing python (https://www.luxoft.com/careers/jobs/senior-test-automation-engineer-28419)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G233" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -13718,9 +13718,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>https://www.yodo1.com/en/careers</t>
+        </is>
+      </c>
       <c r="E427" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -1339,7 +1339,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['backend engineer - python (remote - india)remotefull-timeopen nowbuild backend systems that make complex workflows reliable, maintainable, and easier to evolve. you’ll work on production python services, modernize existing applications, and deliver apis and integrations used by real teams. the role is focused on backend development using pytho...view role (https://axelerant.com/careers/careers/backend-engineer-python-remote-india)']</t>
+          <t>['backend engineer - python (remote - india)remotefull-timeopen nowbuild backend systems that make complex workflows reliable, maintainable, and easier to evolve. you’ll work on production python services, modernize existing applications, and deliver apis and integrations used by real teams.view role (https://axelerant.com/careers/careers/backend-engineer-python-remote-india)']</t>
         </is>
       </c>
       <c r="G30" t="b">
@@ -4403,9 +4403,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://envato.com/careers</t>
+        </is>
+      </c>
       <c r="E128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -9201,9 +9205,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>https://www.parabol.co/join</t>
+        </is>
+      </c>
       <c r="E282" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -4000,7 +4000,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://doist.com/careers</t>
+          <t>https://doist.com/jobs</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://fly.io/jobs</t>
+          <t>https://fly.io/careers</t>
         </is>
       </c>
       <c r="E151" t="b">
@@ -7674,11 +7674,11 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['senior genai fullstack engineer (react &amp; python)remote india, indiafront-end react (https://www.luxoft.com/careers/jobs/senior-genai-fullstack-engineer-react-python-28556)', 'senior genai fullstack engineer (react &amp; python)remote india, indiafront-end react (https://www.luxoft.com/careers/jobs/senior-genai-fullstack-engineer-react-python-28555)']</t>
         </is>
       </c>
       <c r="G233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -4000,7 +4000,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://doist.com/jobs</t>
+          <t>https://doist.com/careers</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -4599,11 +4599,11 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>['data scientist, trust and safety analyticsciudad de méxico, cdmx, mexico city, mexico, 06500analytics (https://careers.etsy.com/jobs/data-scientist-trust-and-safety-analytics-cdmx-mexico-city-mexico)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>['senior genai fullstack engineer (react &amp; python)remote india, indiafront-end react (https://www.luxoft.com/careers/jobs/senior-genai-fullstack-engineer-react-python-28556)', 'senior genai fullstack engineer (react &amp; python)remote india, indiafront-end react (https://www.luxoft.com/careers/jobs/senior-genai-fullstack-engineer-react-python-28555)']</t>
+          <t>['senior genai engineer (azure)remote morocco, moroccopython (https://www.luxoft.com/careers/jobs/senior-genai-engineer-azure-28615)', 'senior genai engineer (azure)remote morocco, moroccopython (https://www.luxoft.com/careers/jobs/senior-genai-engineer-azure-28614)', 'senior genai engineer (azure)remote morocco, moroccopython (https://www.luxoft.com/careers/jobs/senior-genai-engineer-azure-28613)']</t>
         </is>
       </c>
       <c r="G233" t="b">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -7674,7 +7674,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>['senior genai engineer (azure)remote morocco, moroccopython (https://www.luxoft.com/careers/jobs/senior-genai-engineer-azure-28615)', 'senior genai engineer (azure)remote morocco, moroccopython (https://www.luxoft.com/careers/jobs/senior-genai-engineer-azure-28614)', 'senior genai engineer (azure)remote morocco, moroccopython (https://www.luxoft.com/careers/jobs/senior-genai-engineer-azure-28613)']</t>
+          <t>['data/ai engineer with pythonremote poland, polandsolution/integration architecture (https://www.luxoft.com/careers/jobs/dataai-engineer-with-python-28642)', 'data/ai engineer with pythonlos angeles, united states of americasolution/integration architecture (https://www.luxoft.com/careers/jobs/dataai-engineer-with-python-28641)', 'data/ai engineer with pythonlondon, united kingdom of great britain and northern irelandsolution/integration architecture (https://www.luxoft.com/careers/jobs/dataai-engineer-with-python-28640)', 'data/ai engineer with pythonirvine, united states of americasolution/integration architecture (https://www.luxoft.com/careers/jobs/dataai-engineer-with-python-28639)']</t>
         </is>
       </c>
       <c r="G233" t="b">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>['senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)']</t>
+          <t>['senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)']</t>
         </is>
       </c>
       <c r="G262" t="b">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://www.skyrocketventures.com/careers</t>
+          <t>https://www.skyrocketventures.com/jobs</t>
         </is>
       </c>
       <c r="E357" t="b">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -1618,13 +1618,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://bebanjo.com/careers</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -7674,11 +7670,11 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>['data/ai engineer with pythonremote poland, polandsolution/integration architecture (https://www.luxoft.com/careers/jobs/dataai-engineer-with-python-28642)', 'data/ai engineer with pythonlos angeles, united states of americasolution/integration architecture (https://www.luxoft.com/careers/jobs/dataai-engineer-with-python-28641)', 'data/ai engineer with pythonlondon, united kingdom of great britain and northern irelandsolution/integration architecture (https://www.luxoft.com/careers/jobs/dataai-engineer-with-python-28640)', 'data/ai engineer with pythonirvine, united states of americasolution/integration architecture (https://www.luxoft.com/careers/jobs/dataai-engineer-with-python-28639)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G233" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -11534,7 +11530,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://www.skyrocketventures.com/jobs</t>
+          <t>https://www.skyrocketventures.com/careers</t>
         </is>
       </c>
       <c r="E357" t="b">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -1618,9 +1618,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://bebanjo.com/careers</t>
+        </is>
+      </c>
       <c r="E39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -8591,7 +8595,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>['senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)']</t>
+          <t>['senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'senior software engineer - react &amp; pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7831952003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)', 'tech lead - react &amp; pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/8043410003)']</t>
         </is>
       </c>
       <c r="G262" t="b">
@@ -9201,13 +9205,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>https://www.parabol.co/join</t>
-        </is>
-      </c>
+      <c r="D282" t="inlineStr"/>
       <c r="E282" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -9926,7 +9926,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>['for data analysts / scientists (https://quicktrials.com/#data-analysts)', 'for data analysts / scientists (https://quicktrials.com/#data-analysts)']</t>
+          <t>['for data analysts / scientists (https://www.quicktrials.com/#data-analysts)', 'for data analysts / scientists (https://www.quicktrials.com/#data-analysts)']</t>
         </is>
       </c>
       <c r="G305" t="b">
@@ -11590,13 +11590,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>https://smile.io/careers</t>
-        </is>
-      </c>
+      <c r="D359" t="inlineStr"/>
       <c r="E359" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -11590,9 +11590,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>https://smile.io/careers</t>
+        </is>
+      </c>
       <c r="E359" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -9052,9 +9052,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>https://www.optoro.com/careers</t>
+        </is>
+      </c>
       <c r="E277" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -10513,11 +10517,11 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>['data scientist, enterprisefoster city, ca·full-timeview job (https://replit.com/careers/jobs/c05749db-f413-4091-a95c-c8e0aa1b5630)', 'data scientist, growthfoster city, ca·full-timeview job (https://replit.com/careers/jobs/1066b974-3cd8-42cf-a11c-a4217c06f70f)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G324" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -9515,13 +9515,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>https://platform.sh/careers</t>
-        </is>
-      </c>
+      <c r="D292" t="inlineStr"/>
       <c r="E292" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -9984,7 +9980,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://rackspace.com/careers</t>
+          <t>https://rackspace.com/jobs</t>
         </is>
       </c>
       <c r="E307" t="b">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -7674,11 +7674,11 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['lead pyspark developerwroclaw, polandpython (https://www.luxoft.com/careers/jobs/lead-pyspark-developer-28773)', 'lead pyspark developerwarsaw, polandpython (https://www.luxoft.com/careers/jobs/lead-pyspark-developer-28772)', 'lead pyspark developerkrakow, polandpython (https://www.luxoft.com/careers/jobs/lead-pyspark-developer-28771)', 'lead pyspark developergdansk, polandpython (https://www.luxoft.com/careers/jobs/lead-pyspark-developer-28770)']</t>
         </is>
       </c>
       <c r="G233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>['senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'senior software engineer - react &amp; pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7831952003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)', 'tech lead - react &amp; pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/8043410003)']</t>
+          <t>['senior software engineer - python &amp; aipermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7677599003)', 'senior software engineer - python &amp; aipermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7614572003)', 'senior software engineer - react &amp; pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7831952003)', 'tech lead - pythonpermanentcanadaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7792463003)', 'tech lead - pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/7561009003)', 'tech lead - python &amp; aipermanentukremote (https://job-boards.greenhouse.io/nearform/jobs/7692056003)', 'tech lead - react &amp; pythonpermanentusaremote + travel (https://job-boards.greenhouse.io/nearform/jobs/8043410003)']</t>
         </is>
       </c>
       <c r="G262" t="b">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://rackspace.com/jobs</t>
+          <t>https://rackspace.com/careers</t>
         </is>
       </c>
       <c r="E307" t="b">

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -7259,13 +7259,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>https://leadiq.com/careers</t>
-        </is>
-      </c>
+      <c r="D220" t="inlineStr"/>
       <c r="E220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -7674,7 +7670,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>['lead pyspark developerwroclaw, polandpython (https://www.luxoft.com/careers/jobs/lead-pyspark-developer-28773)', 'lead pyspark developerwarsaw, polandpython (https://www.luxoft.com/careers/jobs/lead-pyspark-developer-28772)', 'lead pyspark developerkrakow, polandpython (https://www.luxoft.com/careers/jobs/lead-pyspark-developer-28771)', 'lead pyspark developergdansk, polandpython (https://www.luxoft.com/careers/jobs/lead-pyspark-developer-28770)']</t>
+          <t>['senior python developer with flowablezurich, switzerlandpython (https://www.luxoft.com/careers/jobs/senior-python-developer-with-flowable-28821)']</t>
         </is>
       </c>
       <c r="G233" t="b">
@@ -7763,13 +7759,9 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>https://www.mariadb.com/careers</t>
-        </is>
-      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>

--- a/remote_companies_with_python_jobs_cached.xlsx
+++ b/remote_companies_with_python_jobs_cached.xlsx
@@ -7259,9 +7259,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>https://leadiq.com/careers</t>
+        </is>
+      </c>
       <c r="E220" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -7670,11 +7674,11 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>['senior python developer with flowablezurich, switzerlandpython (https://www.luxoft.com/careers/jobs/senior-python-developer-with-flowable-28821)']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G233" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -7759,9 +7763,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>https://www.mariadb.com/careers</t>
+        </is>
+      </c>
       <c r="E236" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -9507,9 +9515,13 @@
           <t>worldwide</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>https://platform.sh/careers</t>
+        </is>
+      </c>
       <c r="E292" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
